--- a/Result/checksun_type/石灰石.xlsx
+++ b/Result/checksun_type/石灰石.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>15.61</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1529519.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1211570.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1211570.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1455383.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1488562.2</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1488562.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>7424.0549043559</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1529519</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1529519.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>15.61</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>552889.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1531761.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1531761.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1383918.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1525316.78</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1525316.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-11250.54924079753</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>552889</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>552889.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>15.45</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>15.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1602674.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1702430.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1702430.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1381594.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1543293.42</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1543293.42</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>67112.17873901175</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1602674</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1602674.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>15.48</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>15.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1670308.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1614423.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1614423.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1303882.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1523738.54</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1523738.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>64185.10518377437</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1670308</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1670308.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>15.54</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>15.63</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15.63</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>702461.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1603478.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1603478.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1184677.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1500194.58</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1500194.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>50464.74634830048</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>702461</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>702461.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>15.58</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>15.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3130474.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1699196.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1699196.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1213694.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1492008.92</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1492008.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>132759.8142137555</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3130474</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3130474.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>15.61</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>15.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1406236.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1236075.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1236075.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1008882.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1439500.94</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1439500.94</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-14561.47505751392</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1406236</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1406236.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>15.59</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>15.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1162637.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1060757.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1060757.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>930042.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1427734.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1427734.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-39760.62133584497</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1162637</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1162637.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>15.55</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1615584.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>993341.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>993341.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>948198.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1422825.74</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1422825.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-48239.48668575194</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1615584</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1615584.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>15.49</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1181050.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>765877.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>765877.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1338803.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1439931.86</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1439931.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-107159.3483754136</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1181050</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1181050.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>814870.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>728193.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>728193.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1376350.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1469097.32</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1469097.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-140946.2454900942</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>814870</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>814870.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15.01</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2296179.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1772771.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1772771.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2871804.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2127351.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2127351.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-113079.6313257013</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2296179</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2296179.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>15.01</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2724161.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1588940.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1588940</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2969573.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2187633.46</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2187633.46</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-124878.8330158251</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2724161</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2724161.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,21 +6647,17 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AM15" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AO15" t="inlineStr">
         <is>
           <t>15.01</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
       <c r="AP15" t="inlineStr">
         <is>
           <t>32.29</t>
@@ -6780,20 +6698,16 @@
           <t>1090295.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1616637.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1616637.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2881734.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2369216.76</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2369216.76</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-183130.0913940081</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1090295</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1090295.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15.02</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1497444.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2212682.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2212682.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3107504.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2380023.54</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2380023.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-84748.74295591237</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1497444</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1497444.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>15.03</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1255777.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3689238.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3689238.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3145706.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2414310.08</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2414310.08</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>15199.67420407897</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1255777</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1255777.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>15.04</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1377023.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>3970837.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>3970837.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>3186018.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2461469.72</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2461469.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>183333.1746396348</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1377023</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1377023.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,21 +8367,17 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AM19" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="AO19" t="inlineStr">
         <is>
           <t>14.97</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>15.05</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
       <c r="AP19" t="inlineStr">
         <is>
           <t>48.84</t>
@@ -8524,20 +8418,16 @@
           <t>2862648.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>4350207.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>4350207</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>3555590.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2528642.34</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2528642.34</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>403985.6333104419</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2862648</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2862648.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,21 +8797,17 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AM20" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="AO20" t="inlineStr">
         <is>
           <t>14.97</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
       <c r="AP20" t="inlineStr">
         <is>
           <t>61.87</t>
@@ -8960,20 +8848,16 @@
           <t>4070520.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>4146831.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>4146831</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>3375587.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2521002.36</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2521002.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>545601.2659362219</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>4070520</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>4070520.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>8880223.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>4002326.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>4002326.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3146122.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2462772.2</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2462772.2</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>599008.6959039001</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>8880223</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>8880223.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,21 +9657,17 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AM22" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AO22" t="inlineStr">
         <is>
           <t>14.96</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
       <c r="AP22" t="inlineStr">
         <is>
           <t>24.37</t>
@@ -9832,20 +9708,16 @@
           <t>2663774.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2602175.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2602175.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2428155.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2387559.66</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2387559.66</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>138586.5352897295</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2663774</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2663774.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,21 +10087,17 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AM23" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AO23" t="inlineStr">
         <is>
           <t>14.96</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
       <c r="AP23" t="inlineStr">
         <is>
           <t>10.98</t>
@@ -10268,20 +10138,16 @@
           <t>3273870.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2401200.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2401200.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2370937.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2438206.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2438206.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>141939.1795805674</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3273870</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3273870.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>21.12</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>22.5</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>671687205.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>626195530.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>626195530.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>622132821.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>733146356.66</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>733146356.66</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>21189677.43851745</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>671687205</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>671687205.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>20.81</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>22.5</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>494560639.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>640193393.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>640193393.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>603452151.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>734438326.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>734438326</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>18607123.49500573</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>494560639</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>494560639.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>20.74</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>21.57</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>22.54</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>22.54</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>952963874.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>684968154.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>684968154</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>608460649.9</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>745292054.98</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>745292054.98</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>33231066.95088148</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>952963874</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>952963874.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>20.8</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>22.56</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>508895219.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>572334943.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>572334943.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>541620112.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>742408659.92</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>742408659.92</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>3820958.603886724</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>508895219</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>508895219.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>20.99</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>22.6</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>502870717.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>585463875.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>585463875.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>527086711.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>747869455.14</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>747869455.14</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>9248839.765184045</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>502870717</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>502870717.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>21.23</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>22.64</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>22.64</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>741676517.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>618070111.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>618070111.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>508904183.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>743559492.34</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>743559492.34</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>17318122.36113799</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>741676517</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>741676517.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>21.6</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>22.68</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>718434443.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>566710909.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>566710909.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>472748946.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>736966797.76</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>736966797.76</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>2640828.842460155</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>718434443</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>718434443.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>21.83</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>22.71</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>22.71</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>389797823.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>531953145.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>531953145.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>473420250.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>729928690.36</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>729928690.36</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-15930826.42859614</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>389797823</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>389797823.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>21.91</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>22.24</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>22.72</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>574539878.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>510905281.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>510905281.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>532030878.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>733920278.26</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>733920278.26</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-6681738.014798105</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>574539878</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>574539878.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>21.96</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>22.74</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>22.74</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>665901898.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>468709547.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>468709547.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>524403302.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>731032785.28</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>731032785.28</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-13023912.6731295</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>665901898</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>665901898.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>21.88</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>22.75</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>484880504.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>399738255.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>399738255.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>517022636.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>736449789.18</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>736449789.1799999</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-31407810.30384827</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>484880504</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>484880504.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/石灰石.xlsx
+++ b/Result/checksun_type/石灰石.xlsx
@@ -1008,62 +1008,62 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-113.36</t>
+          <t>-105.66</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1650.654739491101</t>
+          <t>-1650.654739498319</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-109354.2346517846</t>
+          <t>-109354.234651786</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1505,62 +1505,62 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.80</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-112.92</t>
+          <t>-105.48</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>17931.81433547136</t>
+          <t>17931.81433546308</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-49249.71590493829</t>
+          <t>-49249.71590493969</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2002,62 +2002,62 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>30146.63801554585</t>
+          <t>30146.63801553632</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-19585.05641283817</t>
+          <t>-19585.0564128398</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2499,62 +2499,62 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-113.45</t>
+          <t>-105.70</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>39188.76427525203</t>
+          <t>39188.76427524107</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-52467.39798080828</t>
+          <t>-52467.39798081038</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2996,62 +2996,62 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-106.12</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>55853.52104908118</t>
+          <t>55853.52104906861</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-28235.44315002207</t>
+          <t>-28235.44315002463</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -3493,62 +3493,62 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-115.67</t>
+          <t>-106.64</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>71142.42363073632</t>
+          <t>71142.42363072193</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-80307.6704221128</t>
+          <t>-80307.6704221156</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -3990,62 +3990,62 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-106.98</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>98678.80436761798</t>
+          <t>98678.80436760146</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-63218.72115288116</t>
+          <t>-63218.72115288442</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4487,62 +4487,62 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-107.01</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>128114.7180986178</t>
+          <t>128114.7180985989</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2532.017844338436</t>
+          <t>2532.01784433471</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4984,62 +4984,62 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-116.31</t>
+          <t>-106.91</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>150947.9363266686</t>
+          <t>150947.9363266469</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>120719.7514887829</t>
+          <t>120719.7514887787</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5481,62 +5481,62 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-116.45</t>
+          <t>-106.97</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>156443.9699335569</t>
+          <t>156443.9699335321</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>91101.55842767563</t>
+          <t>91101.5584276705</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5978,62 +5978,62 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2024-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2024-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -6187,12 +6187,12 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-117.22</t>
+          <t>-107.30</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>168324.4083891717</t>
+          <t>168324.4083891432</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>129697.1555393911</t>
+          <t>129697.155539385</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6470,67 +6470,67 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-87.17</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>21381.35805974964</t>
+          <t>21381.35805974701</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-339637.0314707565</t>
+          <t>-339637.031470757</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -6967,67 +6967,67 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-86.52</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>87021.0652471144</t>
+          <t>87021.06524711137</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-250527.5853005182</t>
+          <t>-250527.5853005187</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -7464,67 +7464,67 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-85.57</t>
+          <t>-86.75</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>148393.5471648658</t>
+          <t>148393.5471648623</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-138084.7841537301</t>
+          <t>-138084.7841537306</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -7961,67 +7961,67 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-84.67</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>200480.5164955196</t>
+          <t>200480.5164955156</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-63954.82593854284</t>
+          <t>-63954.8259385433</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -8458,67 +8458,67 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8672,12 +8672,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-85.65</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>248559.6696653491</t>
+          <t>248559.6696653445</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-172887.8561333278</t>
+          <t>-172887.8561333283</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -8955,67 +8955,67 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9169,12 +9169,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-85.00</t>
+          <t>-86.22</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>325186.4925378358</t>
+          <t>325186.4925378304</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-76061.04726397293</t>
+          <t>-76061.04726397339</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -9452,67 +9452,67 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-86.00</t>
+          <t>-87.14</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>398140.5906836192</t>
+          <t>398140.5906836129</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>136299.9313802477</t>
+          <t>136299.9313802472</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -9949,67 +9949,67 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-86.96</t>
+          <t>-88.02</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>445747.9832842322</t>
+          <t>445747.9832842249</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>93841.83189412626</t>
+          <t>93841.83189412532</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -10446,67 +10446,67 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-89.19</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>509730.9199006151</t>
+          <t>509730.9199006066</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>299804.0886320192</t>
+          <t>299804.0886320183</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -10943,67 +10943,67 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-89.83</t>
+          <t>-90.66</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>547899.4346767234</t>
+          <t>547899.4346767135</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>635585.8093778668</t>
+          <t>635585.8093778649</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -11440,67 +11440,67 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-91.80</t>
+          <t>-92.46</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>531956.4574583338</t>
+          <t>531956.4574583224</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>840514.7029655799</t>
+          <t>840514.7029655781</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -11937,67 +11937,67 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>34.95</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -12032,12 +12032,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12192,12 +12192,12 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>30618840.01772104</t>
+          <t>30618840.01772266</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-68640250.35247445</t>
+          <t>-68640250.3524741</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -12434,67 +12434,67 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>34.95</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>48665947.35775659</t>
+          <t>48665947.35775843</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-23798193.28764105</t>
+          <t>-23798193.28764057</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -12926,72 +12926,72 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>61841245.65691981</t>
+          <t>61841245.65692189</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>1771378.3509655</t>
+          <t>1771378.350965977</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
@@ -13201,94 +13201,94 @@
       </c>
       <c r="BR26" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>16.67</t>
+        </is>
+      </c>
+      <c r="BV26" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE26" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="CG26" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS26" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT26" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU26" t="inlineStr">
-        <is>
-          <t>16.67</t>
-        </is>
-      </c>
-      <c r="BV26" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW26" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX26" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY26" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ26" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA26" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC26" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD26" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE26" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF26" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="CG26" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH26" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ26" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -13423,72 +13423,72 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>72763039.71254787</t>
+          <t>72763039.71255024</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-3554777.034988403</t>
+          <t>-3554777.034987926</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
@@ -13698,94 +13698,94 @@
       </c>
       <c r="BR27" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU27" t="inlineStr">
+        <is>
+          <t>18.92</t>
+        </is>
+      </c>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW27" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX27" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ27" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC27" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD27" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE27" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF27" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="CG27" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI27" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS27" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT27" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU27" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="BV27" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW27" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX27" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY27" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ27" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA27" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB27" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC27" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD27" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE27" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF27" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="CG27" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH27" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ27" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
@@ -13858,12 +13858,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -13920,72 +13920,72 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14180,12 +14180,12 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>86639006.39391811</t>
+          <t>86639006.39392082</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>5832399.164898872</t>
+          <t>5832399.164899349</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
@@ -14195,94 +14195,94 @@
       </c>
       <c r="BR28" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS28" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT28" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU28" t="inlineStr">
+        <is>
+          <t>19.37</t>
+        </is>
+      </c>
+      <c r="BV28" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW28" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX28" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY28" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ28" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA28" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC28" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD28" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE28" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF28" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="CG28" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS28" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT28" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU28" t="inlineStr">
-        <is>
-          <t>19.37</t>
-        </is>
-      </c>
-      <c r="BV28" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW28" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX28" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY28" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ28" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA28" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB28" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC28" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD28" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE28" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF28" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="CG28" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH28" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ28" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
@@ -14355,12 +14355,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -14417,72 +14417,72 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>101331116.7991943</t>
+          <t>101331116.7991975</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>17182923.94456267</t>
+          <t>17182923.94456339</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
@@ -14692,94 +14692,94 @@
       </c>
       <c r="BR29" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS29" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT29" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU29" t="inlineStr">
+        <is>
+          <t>18.69</t>
+        </is>
+      </c>
+      <c r="BV29" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW29" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX29" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ29" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA29" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC29" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD29" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE29" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF29" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="CG29" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH29" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI29" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS29" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT29" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU29" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
-      </c>
-      <c r="BV29" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW29" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX29" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY29" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ29" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA29" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB29" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC29" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD29" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH29" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ29" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="CP29" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ29" t="inlineStr">
@@ -14852,12 +14852,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -14914,72 +14914,72 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -15014,12 +15014,12 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>116630788.2273092</t>
+          <t>116630788.2273128</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>57971406.52463365</t>
+          <t>57971406.5246346</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
@@ -15189,94 +15189,94 @@
       </c>
       <c r="BR30" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS30" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT30" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU30" t="inlineStr">
+        <is>
+          <t>17.34</t>
+        </is>
+      </c>
+      <c r="BV30" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW30" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX30" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY30" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ30" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA30" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC30" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD30" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE30" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="CF30" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="CG30" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS30" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT30" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU30" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
-      </c>
-      <c r="BV30" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW30" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX30" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY30" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ30" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA30" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC30" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD30" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="CG30" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH30" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ30" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="CP30" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ30" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -15411,72 +15411,72 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>127296130.3550684</t>
+          <t>127296130.3550724</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>94147340.0488553</t>
+          <t>94147340.04885626</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
@@ -15686,94 +15686,94 @@
       </c>
       <c r="BR31" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS31" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT31" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU31" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="BV31" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW31" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX31" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY31" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ31" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA31" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC31" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD31" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE31" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF31" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="CG31" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT31" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU31" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="BV31" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW31" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX31" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY31" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ31" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA31" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC31" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD31" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE31" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="CG31" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH31" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ31" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="CP31" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ31" t="inlineStr">
@@ -15846,12 +15846,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -15908,72 +15908,72 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -16008,12 +16008,12 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -16168,12 +16168,12 @@
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>133323183.1380162</t>
+          <t>133323183.1380208</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>133094332.7959986</t>
+          <t>133094332.7959998</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
@@ -16183,94 +16183,94 @@
       </c>
       <c r="BR32" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS32" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT32" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU32" t="inlineStr">
+        <is>
+          <t>15.77</t>
+        </is>
+      </c>
+      <c r="BV32" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW32" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX32" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY32" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ32" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA32" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC32" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD32" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE32" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF32" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="CG32" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH32" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI32" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT32" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU32" t="inlineStr">
-        <is>
-          <t>15.77</t>
-        </is>
-      </c>
-      <c r="BV32" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW32" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX32" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY32" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ32" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA32" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB32" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC32" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD32" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH32" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ32" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="CP32" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ32" t="inlineStr">
@@ -16343,12 +16343,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -16405,72 +16405,72 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>133364792.2911103</t>
+          <t>133364792.2911156</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>203187442.9063461</t>
+          <t>203187442.9063473</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -16680,94 +16680,94 @@
       </c>
       <c r="BR33" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS33" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT33" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU33" t="inlineStr">
+        <is>
+          <t>15.77</t>
+        </is>
+      </c>
+      <c r="BV33" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW33" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX33" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY33" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ33" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA33" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC33" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD33" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE33" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF33" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="CG33" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH33" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI33" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT33" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU33" t="inlineStr">
-        <is>
-          <t>15.77</t>
-        </is>
-      </c>
-      <c r="BV33" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW33" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX33" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY33" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ33" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA33" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC33" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="CG33" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH33" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ33" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="CP33" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ33" t="inlineStr">
@@ -16840,12 +16840,12 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -16902,72 +16902,72 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -17002,12 +17002,12 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
@@ -17162,12 +17162,12 @@
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>120669764.906522</t>
+          <t>120669764.906528</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>150759058.674473</t>
+          <t>150759058.6744742</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
@@ -17177,94 +17177,94 @@
       </c>
       <c r="BR34" t="inlineStr">
         <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="BS34" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="BT34" t="inlineStr">
+        <is>
+          <t>2025/12/18</t>
+        </is>
+      </c>
+      <c r="BU34" t="inlineStr">
+        <is>
+          <t>17.79</t>
+        </is>
+      </c>
+      <c r="BV34" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BW34" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="BX34" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="BY34" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ34" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="CA34" t="inlineStr">
+        <is>
+          <t>8.369476242998935</t>
+        </is>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>-14.04431343802255</t>
+        </is>
+      </c>
+      <c r="CC34" t="inlineStr">
+        <is>
+          <t>-2.74162924434136</t>
+        </is>
+      </c>
+      <c r="CD34" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE34" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF34" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="CG34" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="CH34" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="CI34" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>2025/12/18</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>8.369476242998935</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>-14.04431343802255</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>-2.74162924434136</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>3.88</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CJ34" t="inlineStr">
         <is>
           <t>22.64%</t>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="CP34" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ34" t="inlineStr">
@@ -17337,12 +17337,12 @@
       </c>
       <c r="CX34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
